--- a/KaizhongRPA/bin/Debug/config/RpaGroup/采购订单预付.xlsx
+++ b/KaizhongRPA/bin/Debug/config/RpaGroup/采购订单预付.xlsx
@@ -36,10 +36,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>C:\Program Files (x86)\SAP\FrontEnd\SAPgui\saplogon.exe</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>SAP系统标识</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -84,10 +80,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>C:\Program Files (x86)\SAP\FrontEnd\SAPgui\sapshcut.exe</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>00</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -242,9 +234,6 @@
     <t>http://172.16.10.92/login/Login.jsp?logintype=1</t>
   </si>
   <si>
-    <t>rpa123</t>
-  </si>
-  <si>
     <t>OA登录网址</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -289,30 +278,42 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>sa</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReplacePUser</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>离职采购员替换</t>
+  </si>
+  <si>
+    <t>\\172.16.10.115\temp\KaizhongRPA\ZF003\离职采购员替换表.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>WechatKey</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>07d38e8f-a858-4283-9827-0039032c9f95</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rpa123@</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\Program Files (x86)\SAP\FrontEnd\SAPgui\saplogon.exe</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\Program Files (x86)\SAP\FrontEnd\SAPgui\sapshcut.exe</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>\\172.16.10.115\temp\KaizhongRPA\ZF003\采购中VS二级分类配置表.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>sa</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ReplacePUser</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>离职采购员替换</t>
-  </si>
-  <si>
-    <t>\\172.16.10.115\temp\KaizhongRPA\ZF003\离职采购员替换表.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>WechatKey</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>07d38e8f-a858-4283-9827-0039032c9f95</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -320,7 +321,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -348,6 +349,14 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="宋体"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -419,10 +428,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -448,9 +458,16 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -762,7 +779,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>4</v>
@@ -773,10 +790,10 @@
     </row>
     <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>2</v>
@@ -784,10 +801,10 @@
     </row>
     <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>1</v>
@@ -795,40 +812,40 @@
     </row>
     <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="4">
         <v>3601</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="4">
         <v>800</v>
@@ -839,227 +856,231 @@
     </row>
     <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="C9" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B18" s="7">
         <v>3</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B21" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>57</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>69</v>
+        <v>36</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>75</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B21" r:id="rId1"/>
+    <hyperlink ref="B22" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="150" verticalDpi="150" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="150" verticalDpi="150" r:id="rId3"/>
 </worksheet>
 </file>